--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Large & Mid Cap Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Large & Mid Cap Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="266">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Large &amp; Mid Cap Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -52,7 +52,7 @@
     <t>Yield to Call @</t>
   </si>
   <si>
-    <t>Equity &amp; Equity Related Instruments (Note -1)</t>
+    <t>Equity &amp; Equity Related Instruments</t>
   </si>
   <si>
     <t/>
@@ -70,6 +70,15 @@
     <t>Automobiles</t>
   </si>
   <si>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>FSN E-Commerce Ventures Ltd.</t>
   </si>
   <si>
@@ -88,28 +97,169 @@
     <t>Banks</t>
   </si>
   <si>
+    <t>SBI Cards &amp; Payment Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE018E01016</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Alkem Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE540L01014</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Motherson Sumi Wiring India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0FS801015</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Avenue Supermarts Ltd.</t>
+  </si>
+  <si>
+    <t>INE192R01011</t>
+  </si>
+  <si>
+    <t>Reliance Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>Page Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE761H01022</t>
+  </si>
+  <si>
+    <t>Textiles &amp; Apparels</t>
+  </si>
+  <si>
+    <t>Sona Blw Precision Forgings Ltd.</t>
+  </si>
+  <si>
+    <t>INE073K01018</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE095A01012</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
+  </si>
+  <si>
+    <t>Bharat Forge Ltd.</t>
+  </si>
+  <si>
+    <t>INE465A01025</t>
+  </si>
+  <si>
+    <t>AIA Engineering Ltd.</t>
+  </si>
+  <si>
+    <t>INE212H01026</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A01034</t>
+  </si>
+  <si>
+    <t>PI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE603J01030</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>Shree Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE070A01015</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>Infosys Ltd.</t>
+  </si>
+  <si>
+    <t>INE009A01021</t>
+  </si>
+  <si>
     <t>Bajaj Finserv Ltd.</t>
   </si>
   <si>
     <t>INE918I01026</t>
   </si>
   <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>SBI Cards &amp; Payment Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE018E01016</t>
-  </si>
-  <si>
-    <t>Alkem Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE540L01014</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
+    <t>UPL Ltd.</t>
+  </si>
+  <si>
+    <t>INE628A01036</t>
+  </si>
+  <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Indian Bank</t>
+  </si>
+  <si>
+    <t>INE562A01011</t>
   </si>
   <si>
     <t>United Breweries Ltd.</t>
@@ -121,127 +271,40 @@
     <t>Beverages</t>
   </si>
   <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A01034</t>
-  </si>
-  <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
-    <t>Shree Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE070A01015</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
-    <t>Page Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE761H01022</t>
-  </si>
-  <si>
-    <t>Textiles &amp; Apparels</t>
-  </si>
-  <si>
-    <t>UPL Ltd.</t>
-  </si>
-  <si>
-    <t>INE628A01036</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Motherson Sumi Wiring India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0FS801015</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Reliance Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE002A01018</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>AIA Engineering Ltd.</t>
-  </si>
-  <si>
-    <t>INE212H01026</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE095A01012</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>Infosys Ltd.</t>
-  </si>
-  <si>
-    <t>INE009A01021</t>
-  </si>
-  <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Sona Blw Precision Forgings Ltd.</t>
-  </si>
-  <si>
-    <t>INE073K01018</t>
-  </si>
-  <si>
-    <t>Indian Bank</t>
-  </si>
-  <si>
-    <t>INE562A01011</t>
+    <t>Nestle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE239A01024</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>Gujarat Gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE844O01030</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Hindustan Unilever Ltd.</t>
+  </si>
+  <si>
+    <t>INE030A01027</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
+    <t>Sun TV Network Ltd.</t>
+  </si>
+  <si>
+    <t>INE424H01027</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
   </si>
   <si>
     <t>Interglobe Aviation Ltd.</t>
@@ -253,31 +316,31 @@
     <t>Transport Services</t>
   </si>
   <si>
-    <t>Bharat Forge Ltd.</t>
-  </si>
-  <si>
-    <t>INE465A01025</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
-  </si>
-  <si>
     <t>State Bank Of India</t>
   </si>
   <si>
     <t>INE062A01020</t>
   </si>
   <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
+    <t>Tata Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE155A01022</t>
+  </si>
+  <si>
+    <t>Star Health &amp; Allied Insurance</t>
+  </si>
+  <si>
+    <t>INE575P01011</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>ACC Ltd.</t>
+  </si>
+  <si>
+    <t>INE012A01025</t>
   </si>
   <si>
     <t>Syngene International Ltd.</t>
@@ -289,151 +352,331 @@
     <t>Healthcare Services</t>
   </si>
   <si>
-    <t>Gujarat Gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE844O01030</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>ACC Ltd.</t>
-  </si>
-  <si>
-    <t>INE012A01025</t>
-  </si>
-  <si>
-    <t>Berger Paints India Ltd.</t>
-  </si>
-  <si>
-    <t>INE463A01038</t>
+    <t>TVS Motor Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE494B01023</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Adani Wilmar Ltd</t>
+  </si>
+  <si>
+    <t>INE699H01024</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>Kalpataru Projects International Ltd</t>
+  </si>
+  <si>
+    <t>INE220B01022</t>
+  </si>
+  <si>
+    <t>Sun Pharmaceutical Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE044A01036</t>
+  </si>
+  <si>
+    <t>Gland Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE068V01023</t>
+  </si>
+  <si>
+    <t>NCC Ltd.</t>
+  </si>
+  <si>
+    <t>INE868B01028</t>
+  </si>
+  <si>
+    <t>Oberoi Realty Ltd.</t>
+  </si>
+  <si>
+    <t>INE093I01010</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Ratnamani Metals &amp; Tubes Ltd.</t>
+  </si>
+  <si>
+    <t>INE703B01027</t>
+  </si>
+  <si>
+    <t>Rategain Travel Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE0CLI01024</t>
+  </si>
+  <si>
+    <t>Hindustan Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE094A01015</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Dabur India Ltd.</t>
+  </si>
+  <si>
+    <t>INE016A01026</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Zee Entertainment Enterprises Ltd.</t>
+  </si>
+  <si>
+    <t>INE256A01028</t>
+  </si>
+  <si>
+    <t>CIE Automotive India Ltd</t>
+  </si>
+  <si>
+    <t>INE536H01010</t>
+  </si>
+  <si>
+    <t>Balkrishna Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE787D01026</t>
+  </si>
+  <si>
+    <t>HCL Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE860A01027</t>
+  </si>
+  <si>
+    <t>Indiamart Intermesh Ltd.</t>
+  </si>
+  <si>
+    <t>INE933S01016</t>
+  </si>
+  <si>
+    <t>HDFC Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>Gujarat Narmada Valley Fertilizers and Chemicals Ltd.</t>
+  </si>
+  <si>
+    <t>INE113A01013</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Zydus Lifesciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
+  </si>
+  <si>
+    <t>MRF Ltd.</t>
+  </si>
+  <si>
+    <t>INE883A01011</t>
+  </si>
+  <si>
+    <t>Tech Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE669C01036</t>
+  </si>
+  <si>
+    <t>Nuvoco Vistas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE118D01016</t>
+  </si>
+  <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
+    <t>Prestige Estates Projects Ltd.</t>
+  </si>
+  <si>
+    <t>INE811K01011</t>
+  </si>
+  <si>
+    <t>UPL Ltd. (Right Share)</t>
+  </si>
+  <si>
+    <t>IN9628A01026</t>
+  </si>
+  <si>
+    <t>NMDC Ltd.</t>
+  </si>
+  <si>
+    <t>INE584A01023</t>
+  </si>
+  <si>
+    <t>Minerals &amp; Mining</t>
+  </si>
+  <si>
+    <t>Suprajit Engineering Ltd.</t>
+  </si>
+  <si>
+    <t>INE399C01030</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>SKF India Ltd.</t>
+  </si>
+  <si>
+    <t>INE640A01023</t>
+  </si>
+  <si>
+    <t>Mphasis Ltd.</t>
+  </si>
+  <si>
+    <t>INE356A01018</t>
+  </si>
+  <si>
+    <t>Pidilite Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE318A01026</t>
+  </si>
+  <si>
+    <t>Tata Communications Ltd.</t>
+  </si>
+  <si>
+    <t>INE151A01013</t>
+  </si>
+  <si>
+    <t>KSB Ltd.</t>
+  </si>
+  <si>
+    <t>INE999A01023</t>
+  </si>
+  <si>
+    <t>Pricol Ltd</t>
+  </si>
+  <si>
+    <t>INE726V01018</t>
+  </si>
+  <si>
+    <t>International Gemmological Institute (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE0Q9301021</t>
+  </si>
+  <si>
+    <t>Commercial Services &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE213A01029</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Container Corporation Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE111A01025</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE726G01019</t>
+  </si>
+  <si>
+    <t>Orient Electric Ltd.</t>
+  </si>
+  <si>
+    <t>INE142Z01019</t>
   </si>
   <si>
     <t>Consumer Durables</t>
   </si>
   <si>
-    <t>Hindustan Unilever Ltd.</t>
-  </si>
-  <si>
-    <t>INE030A01027</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
-  </si>
-  <si>
-    <t>Kalpataru Projects International Ltd</t>
-  </si>
-  <si>
-    <t>INE220B01022</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>Rategain Travel Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE0CLI01024</t>
-  </si>
-  <si>
-    <t>Adani Wilmar Ltd</t>
-  </si>
-  <si>
-    <t>INE699H01024</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>Sun TV Network Ltd.</t>
-  </si>
-  <si>
-    <t>INE424H01027</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Tata Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE155A01022</t>
-  </si>
-  <si>
-    <t>Hindustan Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE094A01015</t>
-  </si>
-  <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>HDFC Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE795G01014</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>NCC Ltd.</t>
-  </si>
-  <si>
-    <t>INE868B01028</t>
-  </si>
-  <si>
-    <t>Star Health &amp; Allied Insurance</t>
-  </si>
-  <si>
-    <t>INE575P01011</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE044A01036</t>
-  </si>
-  <si>
-    <t>HCL Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE860A01027</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
-  </si>
-  <si>
-    <t>Ratnamani Metals &amp; Tubes Ltd.</t>
-  </si>
-  <si>
-    <t>INE703B01027</t>
-  </si>
-  <si>
-    <t>Nestle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE239A01024</t>
-  </si>
-  <si>
-    <t>Food Products</t>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
+  </si>
+  <si>
+    <t>Rain Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE855B01025</t>
+  </si>
+  <si>
+    <t>V-Guard Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE951I01027</t>
+  </si>
+  <si>
+    <t>LIC Housing Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE115A01026</t>
   </si>
   <si>
     <t>Procter &amp; Gamble Hygiene and Health Care Ltd.</t>
@@ -442,217 +685,10 @@
     <t>INE179A01014</t>
   </si>
   <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>CIE Automotive India Ltd</t>
-  </si>
-  <si>
-    <t>INE536H01010</t>
-  </si>
-  <si>
-    <t>Tech Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE669C01036</t>
-  </si>
-  <si>
-    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE213A01029</t>
-  </si>
-  <si>
-    <t>Oil</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Gujarat Narmada Valley Fertilizers and Chemicals Ltd.</t>
-  </si>
-  <si>
-    <t>INE113A01013</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
-    <t>Nuvoco Vistas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE118D01016</t>
-  </si>
-  <si>
-    <t>Dabur India Ltd.</t>
-  </si>
-  <si>
-    <t>INE016A01026</t>
-  </si>
-  <si>
-    <t>Balkrishna Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE787D01026</t>
-  </si>
-  <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
-  </si>
-  <si>
-    <t>Container Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE111A01025</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Zee Entertainment Enterprises Ltd.</t>
-  </si>
-  <si>
-    <t>INE256A01028</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>UPL Ltd. (Right Share)</t>
-  </si>
-  <si>
-    <t>IN9628A01018</t>
-  </si>
-  <si>
-    <t>Delhivery Ltd.</t>
-  </si>
-  <si>
-    <t>INE148O01028</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Orient Electric Ltd.</t>
-  </si>
-  <si>
-    <t>INE142Z01019</t>
-  </si>
-  <si>
-    <t>Dalmia Bharat Ltd.</t>
-  </si>
-  <si>
-    <t>INE00R701025</t>
-  </si>
-  <si>
-    <t>Gland Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE068V01023</t>
-  </si>
-  <si>
-    <t>Tata Communications Ltd.</t>
-  </si>
-  <si>
-    <t>INE151A01013</t>
-  </si>
-  <si>
-    <t>Pricol Ltd</t>
-  </si>
-  <si>
-    <t>INE726V01018</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE115A01026</t>
-  </si>
-  <si>
-    <t>International Gemmological Institute (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE0Q9301021</t>
-  </si>
-  <si>
-    <t>Commercial Services &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Indiamart Intermesh Ltd.</t>
-  </si>
-  <si>
-    <t>INE933S01016</t>
-  </si>
-  <si>
-    <t>3M India Ltd.</t>
-  </si>
-  <si>
-    <t>INE470A01017</t>
-  </si>
-  <si>
-    <t>Diversified</t>
-  </si>
-  <si>
-    <t>KSB Ltd.</t>
-  </si>
-  <si>
-    <t>INE999A01023</t>
-  </si>
-  <si>
-    <t>Rain Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE855B01025</t>
-  </si>
-  <si>
-    <t>Sapphire Foods India Ltd</t>
-  </si>
-  <si>
-    <t>INE806T01020</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE726G01019</t>
-  </si>
-  <si>
-    <t>Union Bank Of India</t>
-  </si>
-  <si>
-    <t>INE692A01016</t>
+    <t>Sharda Motor Industries Ltd</t>
+  </si>
+  <si>
+    <t>INE597I01028</t>
   </si>
   <si>
     <t>Divgi Torqtransfer Systems Ltd</t>
@@ -661,25 +697,13 @@
     <t>INE753U01022</t>
   </si>
   <si>
-    <t>NMDC Ltd.</t>
-  </si>
-  <si>
-    <t>INE584A01023</t>
-  </si>
-  <si>
-    <t>Minerals &amp; Mining</t>
-  </si>
-  <si>
-    <t>Jindal Steel &amp; Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE749A01030</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
+    <t>Vedant Fashions Ltd.</t>
+  </si>
+  <si>
+    <t>INE825V01034</t>
+  </si>
+  <si>
+    <t>^</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -718,34 +742,28 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X383</t>
+    <t>IN002025X034</t>
   </si>
   <si>
     <t>SOV</t>
   </si>
   <si>
-    <t>182 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002024Y191</t>
-  </si>
-  <si>
-    <t>IN002024X417</t>
-  </si>
-  <si>
     <t>364 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002023Z471</t>
-  </si>
-  <si>
-    <t>IN002024X409</t>
-  </si>
-  <si>
-    <t>IN002024X425</t>
-  </si>
-  <si>
-    <t>IN002024Z040</t>
+    <t>IN002024Z115</t>
+  </si>
+  <si>
+    <t>IN002024X490</t>
+  </si>
+  <si>
+    <t>IN002024X516</t>
+  </si>
+  <si>
+    <t>IN002025X026</t>
+  </si>
+  <si>
+    <t>IN002024Z164</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -769,22 +787,10 @@
     <t>Total Net Assets</t>
   </si>
   <si>
-    <t>Details of Stock Future / Index Future</t>
-  </si>
-  <si>
-    <t>Stock / Index Futures</t>
-  </si>
-  <si>
-    <t>FSN E-Commerce Ventures Ltd. $$</t>
-  </si>
-  <si>
-    <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
-    <t>$$ - Derivatives.</t>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
   </si>
   <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
@@ -793,7 +799,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -812,10 +818,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="177" formatCode="##0.00"/>
     <numFmt numFmtId="178" formatCode="##0.00%"/>
-    <numFmt numFmtId="179" formatCode="##0"/>
+    <numFmt numFmtId="179" formatCode="\^"/>
+    <numFmt numFmtId="180" formatCode="##0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -1005,7 +1012,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1057,7 +1064,7 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -1066,6 +1073,10 @@
       <protection/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -1176,13 +1187,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>157</xdr:row>
+      <xdr:row>150</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>167</xdr:row>
+      <xdr:row>160</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1200,7 +1211,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="30365700"/>
+          <a:off x="666750" y="29032200"/>
           <a:ext cx="3705225" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1215,13 +1226,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>172</xdr:row>
+      <xdr:row>165</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>182</xdr:row>
+      <xdr:row>175</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1239,7 +1250,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="33223200"/>
+          <a:off x="666750" y="31889700"/>
           <a:ext cx="3705225" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1573,19 +1584,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J171"/>
+  <dimension ref="B1:J164"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="55.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.857142857142858" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="36.0" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.142857142857142" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="21" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="55.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="16.857142857142858" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="36.0" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="11.142857142857142" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="22" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1673,10 +1684,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>1739643.6699999997</v>
+        <v>2051555.3000000005</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9340808304203997</v>
+        <v>0.9473095265205994</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1710,10 +1721,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>1739643.6699999997</v>
+        <v>2051555.3000000005</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9340808304203997</v>
+        <v>0.9473095265205994</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1736,13 +1747,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>1015953</v>
+        <v>862457</v>
       </c>
       <c r="G8" s="15">
-        <v>125070.42</v>
+        <v>106246.08</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0671550638729</v>
+        <v>0.0490593276915</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1765,13 +1776,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>48141528</v>
+        <v>2419698</v>
       </c>
       <c r="G9" s="15">
-        <v>81311.04</v>
+        <v>88926.32</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0436589889502</v>
+        <v>0.0410618958674</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1794,13 +1805,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>5937195</v>
+        <v>42254709</v>
       </c>
       <c r="G10" s="15">
-        <v>74381.18</v>
+        <v>85886.92</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0399380836319</v>
+        <v>0.0396584471888</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1823,13 +1834,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>3910516</v>
+        <v>5231000</v>
       </c>
       <c r="G11" s="15">
-        <v>67890.47</v>
+        <v>75629.80</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0364529746459</v>
+        <v>0.0349222026962</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1849,16 +1860,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F12" s="14">
-        <v>7859059</v>
+        <v>8161125</v>
       </c>
       <c r="G12" s="15">
-        <v>61159.20</v>
+        <v>75168.04</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0328386998494</v>
+        <v>0.0347089841459</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1869,25 +1880,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F13" s="14">
-        <v>978623</v>
+        <v>5707695</v>
       </c>
       <c r="G13" s="15">
-        <v>49548.17</v>
+        <v>68047.14</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0266042963727</v>
+        <v>0.0314208951495</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1910,13 +1921,13 @@
         <v>34</v>
       </c>
       <c r="F14" s="14">
-        <v>2245925</v>
+        <v>1176469</v>
       </c>
       <c r="G14" s="15">
-        <v>48197.55</v>
+        <v>59982.27</v>
       </c>
       <c r="H14" s="16">
-        <v>0.025879097142</v>
+        <v>0.0276969262264</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1936,16 +1947,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F15" s="14">
-        <v>2755200</v>
+        <v>98790911</v>
       </c>
       <c r="G15" s="15">
-        <v>46803.96</v>
+        <v>57180.18</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0251308256845</v>
+        <v>0.0264030558876</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1956,25 +1967,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F16" s="14">
-        <v>847348</v>
+        <v>1400000</v>
       </c>
       <c r="G16" s="15">
-        <v>44013.80</v>
+        <v>56029.40</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0236326826942</v>
+        <v>0.0258716810536</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1985,25 +1996,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F17" s="14">
-        <v>153895</v>
+        <v>3894790</v>
       </c>
       <c r="G17" s="15">
-        <v>42776.50</v>
+        <v>55341.07</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0229683292801</v>
+        <v>0.0255538433787</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -2014,25 +2025,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F18" s="14">
-        <v>1157695</v>
+        <v>114512</v>
       </c>
       <c r="G18" s="15">
-        <v>42425.47</v>
+        <v>53110.67</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0227798479264</v>
+        <v>0.0245239519749</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -2043,25 +2054,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F19" s="14">
-        <v>4225379</v>
+        <v>9667230</v>
       </c>
       <c r="G19" s="15">
-        <v>41666.46</v>
+        <v>52584.90</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0223723065986</v>
+        <v>0.0242811766864</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -2072,25 +2083,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="F20" s="14">
-        <v>92147</v>
+        <v>5463820</v>
       </c>
       <c r="G20" s="15">
-        <v>41211.41</v>
+        <v>44636.68</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0221279729519</v>
+        <v>0.0206110711207</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2101,25 +2112,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F21" s="14">
-        <v>6688530</v>
+        <v>9197500</v>
       </c>
       <c r="G21" s="15">
-        <v>40382</v>
+        <v>40059.71</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0216826311874</v>
+        <v>0.0184976465966</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2130,25 +2141,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F22" s="14">
-        <v>65460199</v>
+        <v>3129437</v>
       </c>
       <c r="G22" s="15">
-        <v>36742.81</v>
+        <v>38833.18</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0197286117086</v>
+        <v>0.0179312940573</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2171,13 +2182,13 @@
         <v>57</v>
       </c>
       <c r="F23" s="14">
-        <v>2718986</v>
+        <v>1105154</v>
       </c>
       <c r="G23" s="15">
-        <v>34397.89</v>
+        <v>38657.18</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0184695350031</v>
+        <v>0.0178500257256</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2197,16 +2208,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F24" s="14">
-        <v>887360</v>
+        <v>1930200</v>
       </c>
       <c r="G24" s="15">
-        <v>31655.68</v>
+        <v>37540.46</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0169971381909</v>
+        <v>0.0173343781608</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2217,25 +2228,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="D25" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="F25" s="14">
-        <v>835139</v>
+        <v>921038</v>
       </c>
       <c r="G25" s="15">
-        <v>30738.13</v>
+        <v>35217.73</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0165044707092</v>
+        <v>0.0162618532055</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2246,25 +2257,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="F26" s="14">
-        <v>3039804</v>
+        <v>117151</v>
       </c>
       <c r="G26" s="15">
-        <v>30130.54</v>
+        <v>34670.84</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0161782325367</v>
+        <v>0.0160093257172</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2287,13 +2298,13 @@
         <v>68</v>
       </c>
       <c r="F27" s="14">
-        <v>6798457</v>
+        <v>971285</v>
       </c>
       <c r="G27" s="15">
-        <v>30008.39</v>
+        <v>33639.48</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0161126455574</v>
+        <v>0.0155330932933</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2313,16 +2324,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F28" s="14">
-        <v>1567596</v>
+        <v>2117596</v>
       </c>
       <c r="G28" s="15">
-        <v>29467.67</v>
+        <v>33091.67</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0158223124303</v>
+        <v>0.0152801409933</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2333,25 +2344,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>73</v>
-      </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F29" s="14">
-        <v>5797004</v>
+        <v>1610516</v>
       </c>
       <c r="G29" s="15">
-        <v>29234.29</v>
+        <v>32490.55</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0156970018349</v>
+        <v>0.0150025727003</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2362,25 +2373,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F30" s="14">
-        <v>5177616</v>
+        <v>4500000</v>
       </c>
       <c r="G30" s="15">
-        <v>28774.60</v>
+        <v>28255.50</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0154501767957</v>
+        <v>0.0130470303806</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2391,25 +2402,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="F31" s="14">
-        <v>630000</v>
+        <v>498074</v>
       </c>
       <c r="G31" s="15">
-        <v>27243.41</v>
+        <v>26564.78</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0146280226664</v>
+        <v>0.012266337234</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2420,25 +2431,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F32" s="14">
-        <v>2048569</v>
+        <v>7245000</v>
       </c>
       <c r="G32" s="15">
-        <v>25075.51</v>
+        <v>24191.06</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0134639947295</v>
+        <v>0.01117026755</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2449,25 +2460,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F33" s="14">
-        <v>702256</v>
+        <v>3880052</v>
       </c>
       <c r="G33" s="15">
-        <v>24464.84</v>
+        <v>23924.40</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0131361027878</v>
+        <v>0.0110471367924</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2478,25 +2489,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="D34" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="F34" s="14">
-        <v>3135750</v>
+        <v>1205419</v>
       </c>
       <c r="G34" s="15">
-        <v>24236.21</v>
+        <v>23828.72</v>
       </c>
       <c r="H34" s="16">
-        <v>0.013013342648</v>
+        <v>0.0110029563721</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2519,13 +2530,13 @@
         <v>87</v>
       </c>
       <c r="F35" s="14">
-        <v>7245000</v>
+        <v>920042</v>
       </c>
       <c r="G35" s="15">
-        <v>23473.80</v>
+        <v>22046.05</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0126039757309</v>
+        <v>0.0101798051396</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2548,13 +2559,13 @@
         <v>90</v>
       </c>
       <c r="F36" s="14">
-        <v>2735706</v>
+        <v>4617839</v>
       </c>
       <c r="G36" s="15">
-        <v>20426.15</v>
+        <v>21244.37</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0109675765694</v>
+        <v>0.0098096278886</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2577,13 +2588,13 @@
         <v>93</v>
       </c>
       <c r="F37" s="14">
-        <v>4152680</v>
+        <v>897008</v>
       </c>
       <c r="G37" s="15">
-        <v>20182.02</v>
+        <v>21064.44</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0108364938902</v>
+        <v>0.009726544872</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2603,16 +2614,16 @@
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="F38" s="14">
-        <v>953221</v>
+        <v>3343460</v>
       </c>
       <c r="G38" s="15">
-        <v>19137.34</v>
+        <v>21052.10</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0102755654779</v>
+        <v>0.0097208468537</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2623,25 +2634,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F39" s="14">
-        <v>3913979</v>
+        <v>363128</v>
       </c>
       <c r="G39" s="15">
-        <v>18503.34</v>
+        <v>19354.72</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0099351467722</v>
+        <v>0.0089370784395</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2652,25 +2663,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="F40" s="14">
-        <v>721608</v>
+        <v>2360750</v>
       </c>
       <c r="G40" s="15">
-        <v>17815.06</v>
+        <v>19176.37</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0095655830707</v>
+        <v>0.0088547249909</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2690,16 +2701,16 @@
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F41" s="14">
-        <v>1612020</v>
+        <v>2644731</v>
       </c>
       <c r="G41" s="15">
-        <v>17065.65</v>
+        <v>19028.84</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0091631963479</v>
+        <v>0.0087866027353</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2722,13 +2733,13 @@
         <v>106</v>
       </c>
       <c r="F42" s="14">
-        <v>999924</v>
+        <v>3856647</v>
       </c>
       <c r="G42" s="15">
-        <v>16261.76</v>
+        <v>18421.27</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0087315572418</v>
+        <v>0.0085060561427</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2748,16 +2759,16 @@
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F43" s="14">
-        <v>2307043</v>
+        <v>953221</v>
       </c>
       <c r="G43" s="15">
-        <v>16129.69</v>
+        <v>17947.24</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0086606438373</v>
+        <v>0.0082871718967</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2780,13 +2791,13 @@
         <v>111</v>
       </c>
       <c r="F44" s="14">
-        <v>6000000</v>
+        <v>2762318</v>
       </c>
       <c r="G44" s="15">
-        <v>15999</v>
+        <v>17859.77</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0085904714072</v>
+        <v>0.0082467824594</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2806,16 +2817,16 @@
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F45" s="14">
-        <v>2562557</v>
+        <v>628893</v>
       </c>
       <c r="G45" s="15">
-        <v>15858.38</v>
+        <v>17488.26</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0085149671826</v>
+        <v>0.0080752370166</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2826,25 +2837,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>116</v>
-      </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="F46" s="14">
-        <v>2148137</v>
+        <v>515818</v>
       </c>
       <c r="G46" s="15">
-        <v>15382.81</v>
+        <v>16857.45</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0082596155677</v>
+        <v>0.0077839593102</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2855,25 +2866,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="D47" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>57</v>
-      </c>
       <c r="F47" s="14">
-        <v>4186121</v>
+        <v>6000000</v>
       </c>
       <c r="G47" s="15">
-        <v>14996.78</v>
+        <v>16500</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0080523413832</v>
+        <v>0.007618906099</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2896,13 +2907,13 @@
         <v>121</v>
       </c>
       <c r="F48" s="14">
-        <v>2340269</v>
+        <v>857770</v>
       </c>
       <c r="G48" s="15">
-        <v>13908.22</v>
+        <v>15921.93</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0074678521305</v>
+        <v>0.0073519811869</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2922,16 +2933,16 @@
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F49" s="14">
-        <v>2062494</v>
+        <v>1375695</v>
       </c>
       <c r="G49" s="15">
-        <v>13159.74</v>
+        <v>15665.73</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0070659647601</v>
+        <v>0.0072336803541</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2942,25 +2953,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>126</v>
-      </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="F50" s="14">
-        <v>5199691</v>
+        <v>928522</v>
       </c>
       <c r="G50" s="15">
-        <v>13118.82</v>
+        <v>15576.89</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0070439932562</v>
+        <v>0.0071926583166</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2971,25 +2982,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="D51" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="F51" s="14">
-        <v>2997067</v>
+        <v>952390</v>
       </c>
       <c r="G51" s="15">
-        <v>12984.79</v>
+        <v>15129.67</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0069720274532</v>
+        <v>0.0069861536387</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -3000,25 +3011,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>130</v>
-      </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F52" s="14">
-        <v>712788</v>
+        <v>6507306</v>
       </c>
       <c r="G52" s="15">
-        <v>12430.67</v>
+        <v>15044.24</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0066744993567</v>
+        <v>0.0069467061752</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -3029,25 +3040,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="D53" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>71</v>
-      </c>
       <c r="F53" s="14">
-        <v>719200</v>
+        <v>858923</v>
       </c>
       <c r="G53" s="15">
-        <v>12409.44</v>
+        <v>14999.37</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0066631001625</v>
+        <v>0.0069259873681</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -3067,16 +3078,16 @@
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="F54" s="14">
-        <v>495178</v>
+        <v>2320269</v>
       </c>
       <c r="G54" s="15">
-        <v>12170.98</v>
+        <v>14698.90</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0065350619218</v>
+        <v>0.0067872447793</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -3087,25 +3098,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F55" s="14">
-        <v>412217</v>
+        <v>511204</v>
       </c>
       <c r="G55" s="15">
-        <v>11783.64</v>
+        <v>14513.08</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0063270843486</v>
+        <v>0.0067014420441</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3116,25 +3127,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="F56" s="14">
-        <v>499086</v>
+        <v>3268611</v>
       </c>
       <c r="G56" s="15">
-        <v>11544.86</v>
+        <v>14506.10</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0061988742878</v>
+        <v>0.0066982190159</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3154,16 +3165,16 @@
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="F57" s="14">
-        <v>76886</v>
+        <v>3487209</v>
       </c>
       <c r="G57" s="15">
-        <v>11148.93</v>
+        <v>14334.17</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0059862844169</v>
+        <v>0.0066188300143</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3174,25 +3185,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C58" s="13" t="s">
-        <v>144</v>
-      </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="F58" s="14">
-        <v>8235419</v>
+        <v>1124448</v>
       </c>
       <c r="G58" s="15">
-        <v>11086.52</v>
+        <v>14069.09</v>
       </c>
       <c r="H58" s="16">
-        <v>0.005952774115</v>
+        <v>0.0064964288247</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3203,25 +3214,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C59" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F59" s="14">
-        <v>2310946</v>
+        <v>8282599</v>
       </c>
       <c r="G59" s="15">
-        <v>10733.19</v>
+        <v>13336.64</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0057630578038</v>
+        <v>0.0061582186567</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3232,25 +3243,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C60" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="D60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>71</v>
-      </c>
       <c r="F60" s="14">
-        <v>608269</v>
+        <v>2679102</v>
       </c>
       <c r="G60" s="15">
-        <v>10185.16</v>
+        <v>12938.72</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0054687996598</v>
+        <v>0.0059744783467</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3270,16 +3281,16 @@
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="F61" s="14">
-        <v>3698250</v>
+        <v>9434659</v>
       </c>
       <c r="G61" s="15">
-        <v>9711.97</v>
+        <v>12304.68</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0052147259574</v>
+        <v>0.0056817091817</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3290,25 +3301,25 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C62" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C62" s="13" t="s">
-        <v>154</v>
-      </c>
       <c r="D62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="F62" s="14">
-        <v>330000</v>
+        <v>2720098</v>
       </c>
       <c r="G62" s="15">
-        <v>9616.37</v>
+        <v>12233.64</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0051633946825</v>
+        <v>0.0056489063278</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3319,25 +3330,25 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C63" s="13" t="s">
-        <v>156</v>
-      </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="F63" s="14">
-        <v>1670926</v>
+        <v>490483</v>
       </c>
       <c r="G63" s="15">
-        <v>9264.45</v>
+        <v>12125.72</v>
       </c>
       <c r="H63" s="16">
-        <v>0.004974435454</v>
+        <v>0.0055990740644</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3348,25 +3359,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="F64" s="14">
-        <v>491993</v>
+        <v>719200</v>
       </c>
       <c r="G64" s="15">
-        <v>9143.69</v>
+        <v>11770.43</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0049095948185</v>
+        <v>0.0054350182372</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3377,25 +3388,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F65" s="14">
-        <v>2207289</v>
+        <v>484613</v>
       </c>
       <c r="G65" s="15">
-        <v>7736.55</v>
+        <v>11303.60</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0041540478508</v>
+        <v>0.0052194586049</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3406,25 +3417,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="F66" s="14">
-        <v>1445222</v>
+        <v>1402494</v>
       </c>
       <c r="G66" s="15">
-        <v>7657.51</v>
+        <v>10895.27</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0041116082696</v>
+        <v>0.0050309114577</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3435,25 +3446,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="C67" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F67" s="14">
-        <v>275815</v>
+        <v>1970336</v>
       </c>
       <c r="G67" s="15">
-        <v>7643.52</v>
+        <v>10550.16</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0041040965067</v>
+        <v>0.0048715562648</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3464,25 +3475,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C68" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>167</v>
-      </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F68" s="14">
-        <v>314911</v>
+        <v>2406270</v>
       </c>
       <c r="G68" s="15">
-        <v>7245.47</v>
+        <v>10059.41</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0038903683272</v>
+        <v>0.0046449515273</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3493,25 +3504,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C69" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C69" s="13" t="s">
-        <v>169</v>
-      </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="F69" s="14">
-        <v>880000</v>
+        <v>1056117</v>
       </c>
       <c r="G69" s="15">
-        <v>6864.88</v>
+        <v>9821.89</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0036860150855</v>
+        <v>0.0045352762196</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3522,25 +3533,25 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C70" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C70" s="13" t="s">
-        <v>171</v>
-      </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="F70" s="14">
-        <v>1531779</v>
+        <v>6927</v>
       </c>
       <c r="G70" s="15">
-        <v>6854.71</v>
+        <v>9619.18</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0036805544259</v>
+        <v>0.0044416744951</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3551,25 +3562,25 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C71" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C71" s="13" t="s">
-        <v>173</v>
-      </c>
       <c r="D71" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="F71" s="14">
-        <v>5429102</v>
+        <v>608269</v>
       </c>
       <c r="G71" s="15">
-        <v>5732.59</v>
+        <v>9573.55</v>
       </c>
       <c r="H71" s="16">
-        <v>0.0030780455331</v>
+        <v>0.0044206047566</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3580,25 +3591,25 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C72" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="C72" s="13" t="s">
-        <v>175</v>
-      </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="F72" s="14">
-        <v>381820</v>
+        <v>2635827</v>
       </c>
       <c r="G72" s="15">
-        <v>5664.68</v>
+        <v>9432.31</v>
       </c>
       <c r="H72" s="16">
-        <v>0.003041582072</v>
+        <v>0.0043553869204</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -3609,25 +3620,25 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C73" s="13" t="s">
-        <v>177</v>
-      </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="F73" s="14">
-        <v>2070432</v>
+        <v>491993</v>
       </c>
       <c r="G73" s="15">
-        <v>5449.38</v>
+        <v>9226.84</v>
       </c>
       <c r="H73" s="16">
-        <v>0.002925979316</v>
+        <v>0.0042605107606</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -3638,25 +3649,25 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C74" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>179</v>
-      </c>
       <c r="D74" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="F74" s="14">
-        <v>1634927</v>
+        <v>571810</v>
       </c>
       <c r="G74" s="15">
-        <v>5248.93</v>
+        <v>8386.17</v>
       </c>
       <c r="H74" s="16">
-        <v>0.0028183500896</v>
+        <v>0.0038723298036</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -3667,25 +3678,25 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C75" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="C75" s="13" t="s">
-        <v>181</v>
-      </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F75" s="14">
-        <v>1991796</v>
+        <v>2005714</v>
       </c>
       <c r="G75" s="15">
-        <v>5200.58</v>
+        <v>8220.42</v>
       </c>
       <c r="H75" s="16">
-        <v>0.0027923891362</v>
+        <v>0.0037957944287</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -3696,25 +3707,25 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C76" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="D76" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="D76" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>98</v>
-      </c>
       <c r="F76" s="14">
-        <v>2294011</v>
+        <v>11416742</v>
       </c>
       <c r="G76" s="15">
-        <v>5038.80</v>
+        <v>8125.30</v>
       </c>
       <c r="H76" s="16">
-        <v>0.0027055233031</v>
+        <v>0.0037518725894</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>13</v>
@@ -3734,16 +3745,16 @@
         <v>13</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F77" s="14">
-        <v>257090</v>
+        <v>1857635</v>
       </c>
       <c r="G77" s="15">
-        <v>4798.20</v>
+        <v>7776.99</v>
       </c>
       <c r="H77" s="16">
-        <v>0.0025763360151</v>
+        <v>0.0035910397904</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>13</v>
@@ -3763,16 +3774,16 @@
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="F78" s="14">
-        <v>261954</v>
+        <v>426735</v>
       </c>
       <c r="G78" s="15">
-        <v>3994.14</v>
+        <v>7733.29</v>
       </c>
       <c r="H78" s="16">
-        <v>0.0021446056295</v>
+        <v>0.0035708612331</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>13</v>
@@ -3792,16 +3803,16 @@
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="F79" s="14">
-        <v>237094</v>
+        <v>163166</v>
       </c>
       <c r="G79" s="15">
-        <v>3871.75</v>
+        <v>7662.28</v>
       </c>
       <c r="H79" s="16">
-        <v>0.002078889785</v>
+        <v>0.0035380722317</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>13</v>
@@ -3821,16 +3832,16 @@
         <v>13</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F80" s="14">
-        <v>750990</v>
+        <v>292269</v>
       </c>
       <c r="G80" s="15">
-        <v>3792.50</v>
+        <v>7478.58</v>
       </c>
       <c r="H80" s="16">
-        <v>0.0020363374468</v>
+        <v>0.0034532484105</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>13</v>
@@ -3850,16 +3861,16 @@
         <v>13</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="F81" s="14">
-        <v>620406</v>
+        <v>240536</v>
       </c>
       <c r="G81" s="15">
-        <v>3710.65</v>
+        <v>7473.93</v>
       </c>
       <c r="H81" s="16">
-        <v>0.0019923890697</v>
+        <v>0.0034511012642</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>13</v>
@@ -3879,16 +3890,16 @@
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>196</v>
+        <v>121</v>
       </c>
       <c r="F82" s="14">
-        <v>718059</v>
+        <v>440685</v>
       </c>
       <c r="G82" s="15">
-        <v>3637.69</v>
+        <v>7386.76</v>
       </c>
       <c r="H82" s="16">
-        <v>0.0019532140717</v>
+        <v>0.0034108503524</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>13</v>
@@ -3899,25 +3910,25 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C83" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="C83" s="13" t="s">
-        <v>198</v>
-      </c>
       <c r="D83" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="F83" s="14">
-        <v>169833</v>
+        <v>867370</v>
       </c>
       <c r="G83" s="15">
-        <v>3509.43</v>
+        <v>7339.68</v>
       </c>
       <c r="H83" s="16">
-        <v>0.001884346401</v>
+        <v>0.0033891110737</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>13</v>
@@ -3928,25 +3939,25 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C84" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C84" s="13" t="s">
-        <v>200</v>
-      </c>
       <c r="D84" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="F84" s="14">
-        <v>10375</v>
+        <v>1601259</v>
       </c>
       <c r="G84" s="15">
-        <v>3101.32</v>
+        <v>7201.66</v>
       </c>
       <c r="H84" s="16">
-        <v>0.001665216625</v>
+        <v>0.0033253800786</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>13</v>
@@ -3957,25 +3968,25 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C85" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="D85" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="F85" s="14">
-        <v>441285</v>
+        <v>1842793</v>
       </c>
       <c r="G85" s="15">
-        <v>3100.25</v>
+        <v>7166.62</v>
       </c>
       <c r="H85" s="16">
-        <v>0.0016646421014</v>
+        <v>0.0033092002925</v>
       </c>
       <c r="I85" s="15" t="s">
         <v>13</v>
@@ -3986,25 +3997,25 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C86" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="D86" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="D86" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>157</v>
-      </c>
       <c r="F86" s="14">
-        <v>1900573</v>
+        <v>2928250</v>
       </c>
       <c r="G86" s="15">
-        <v>2754.12</v>
+        <v>7010.23</v>
       </c>
       <c r="H86" s="16">
-        <v>0.0014787917439</v>
+        <v>0.0032369869153</v>
       </c>
       <c r="I86" s="15" t="s">
         <v>13</v>
@@ -4024,16 +4035,16 @@
         <v>13</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>208</v>
+        <v>99</v>
       </c>
       <c r="F87" s="14">
-        <v>868541</v>
+        <v>880000</v>
       </c>
       <c r="G87" s="15">
-        <v>2515.29</v>
+        <v>6902.72</v>
       </c>
       <c r="H87" s="16">
-        <v>0.0013505548363</v>
+        <v>0.0031873439701</v>
       </c>
       <c r="I87" s="15" t="s">
         <v>13</v>
@@ -4044,25 +4055,25 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C88" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C88" s="13" t="s">
-        <v>210</v>
-      </c>
       <c r="D88" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F88" s="14">
-        <v>400790</v>
+        <v>958670</v>
       </c>
       <c r="G88" s="15">
-        <v>2468.87</v>
+        <v>6350.23</v>
       </c>
       <c r="H88" s="16">
-        <v>0.0013256301733</v>
+        <v>0.0029322306713</v>
       </c>
       <c r="I88" s="15" t="s">
         <v>13</v>
@@ -4073,25 +4084,25 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C89" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="D89" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D89" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="F89" s="14">
-        <v>2000000</v>
+        <v>2632346</v>
       </c>
       <c r="G89" s="15">
-        <v>2309.8</v>
+        <v>5972.53</v>
       </c>
       <c r="H89" s="16">
-        <v>0.0012402194422</v>
+        <v>0.0027578269844</v>
       </c>
       <c r="I89" s="15" t="s">
         <v>13</v>
@@ -4111,16 +4122,16 @@
         <v>13</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>54</v>
+        <v>212</v>
       </c>
       <c r="F90" s="14">
-        <v>373010</v>
+        <v>262904</v>
       </c>
       <c r="G90" s="15">
-        <v>2195.91</v>
+        <v>5939.26</v>
       </c>
       <c r="H90" s="16">
-        <v>0.0011790675709</v>
+        <v>0.0027424644992</v>
       </c>
       <c r="I90" s="15" t="s">
         <v>13</v>
@@ -4140,16 +4151,16 @@
         <v>13</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="F91" s="14">
-        <v>3000000</v>
+        <v>3186257</v>
       </c>
       <c r="G91" s="15">
-        <v>1983</v>
+        <v>4495.81</v>
       </c>
       <c r="H91" s="16">
-        <v>0.0010647480967</v>
+        <v>0.0020759487411</v>
       </c>
       <c r="I91" s="15" t="s">
         <v>13</v>
@@ -4160,25 +4171,25 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C92" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="C92" s="13" t="s">
-        <v>219</v>
-      </c>
       <c r="D92" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>145</v>
+        <v>212</v>
       </c>
       <c r="F92" s="14">
-        <v>84989</v>
+        <v>1169550</v>
       </c>
       <c r="G92" s="15">
-        <v>672.73</v>
+        <v>4436.69</v>
       </c>
       <c r="H92" s="16">
-        <v>0.0003612143152</v>
+        <v>0.0020486499697</v>
       </c>
       <c r="I92" s="15" t="s">
         <v>13</v>
@@ -4189,25 +4200,25 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C93" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="C93" s="13" t="s">
-        <v>221</v>
-      </c>
       <c r="D93" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="F93" s="14">
-        <v>153177</v>
+        <v>620406</v>
       </c>
       <c r="G93" s="15">
-        <v>249.60</v>
+        <v>3700.41</v>
       </c>
       <c r="H93" s="16">
-        <v>0.0001340197301</v>
+        <v>0.0017086712919</v>
       </c>
       <c r="I93" s="15" t="s">
         <v>13</v>
@@ -4218,6 +4229,27 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F94" s="14">
+        <v>21800</v>
+      </c>
+      <c r="G94" s="15">
+        <v>2961.31</v>
+      </c>
+      <c r="H94" s="16">
+        <v>0.0013673904739</v>
+      </c>
+      <c r="I94" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J94" s="11" t="s">
@@ -4225,28 +4257,28 @@
       </c>
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="9" t="s">
+      <c r="B95" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="H95" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="I95" s="9" t="s">
+      <c r="C95" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F95" s="14">
+        <v>117465</v>
+      </c>
+      <c r="G95" s="15">
+        <v>2235.83</v>
+      </c>
+      <c r="H95" s="16">
+        <v>0.0010323987165</v>
+      </c>
+      <c r="I95" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J95" s="11" t="s">
@@ -4255,6 +4287,27 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F96" s="14">
+        <v>373010</v>
+      </c>
+      <c r="G96" s="15">
+        <v>2077.67</v>
+      </c>
+      <c r="H96" s="16">
+        <v>0.0009593680384</v>
+      </c>
+      <c r="I96" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J96" s="11" t="s">
@@ -4262,28 +4315,28 @@
       </c>
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="I97" s="9" t="s">
+      <c r="B97" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F97" s="14">
+        <v>11803</v>
+      </c>
+      <c r="G97" s="15">
+        <v>94.11</v>
+      </c>
+      <c r="H97" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="I97" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J97" s="11" t="s">
@@ -4300,7 +4353,7 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="7" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>13</v>
@@ -4315,10 +4368,10 @@
         <v>13</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I99" s="9" t="s">
         <v>13</v>
@@ -4337,7 +4390,7 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="7" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>13</v>
@@ -4352,10 +4405,10 @@
         <v>13</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I101" s="9" t="s">
         <v>13</v>
@@ -4374,7 +4427,7 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
       <c r="B103" s="7" t="s">
-        <v>226</v>
+        <v>14</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>13</v>
@@ -4389,10 +4442,10 @@
         <v>13</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I103" s="9" t="s">
         <v>13</v>
@@ -4411,7 +4464,7 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
       <c r="B105" s="7" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>13</v>
@@ -4426,10 +4479,10 @@
         <v>13</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I105" s="9" t="s">
         <v>13</v>
@@ -4448,7 +4501,7 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
       <c r="B107" s="7" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>13</v>
@@ -4463,10 +4516,10 @@
         <v>13</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I107" s="9" t="s">
         <v>13</v>
@@ -4485,7 +4538,7 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
       <c r="B109" s="7" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>13</v>
@@ -4499,11 +4552,11 @@
       <c r="F109" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G109" s="9">
-        <v>19554.920000000002</v>
-      </c>
-      <c r="H109" s="10">
-        <v>0.0104997800567</v>
+      <c r="G109" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="I109" s="9" t="s">
         <v>13</v>
@@ -4522,7 +4575,7 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="7" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>13</v>
@@ -4537,10 +4590,10 @@
         <v>13</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I111" s="9" t="s">
         <v>13</v>
@@ -4559,7 +4612,7 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
       <c r="B113" s="7" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>13</v>
@@ -4573,11 +4626,11 @@
       <c r="F113" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G113" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>223</v>
+      <c r="G113" s="9">
+        <v>15330.95</v>
+      </c>
+      <c r="H113" s="10">
+        <v>0.0070790950577</v>
       </c>
       <c r="I113" s="9" t="s">
         <v>13</v>
@@ -4596,7 +4649,7 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
       <c r="B115" s="7" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>13</v>
@@ -4610,11 +4663,11 @@
       <c r="F115" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G115" s="9">
-        <v>19554.920000000002</v>
-      </c>
-      <c r="H115" s="10">
-        <v>0.0104997800567</v>
+      <c r="G115" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="I115" s="9" t="s">
         <v>13</v>
@@ -4625,57 +4678,36 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
       <c r="B116" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="C116" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="D116" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="F116" s="14">
-        <v>5200000</v>
-      </c>
-      <c r="G116" s="15">
-        <v>5150.14</v>
-      </c>
-      <c r="H116" s="16">
-        <v>0.0027653059824</v>
-      </c>
-      <c r="I116" s="15">
-        <v>6.43</v>
+        <v>13</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
-      <c r="B117" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="C117" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="F117" s="14">
-        <v>5000000</v>
-      </c>
-      <c r="G117" s="15">
-        <v>4995.65</v>
-      </c>
-      <c r="H117" s="16">
-        <v>0.0026823544275</v>
-      </c>
-      <c r="I117" s="15">
-        <v>6.37</v>
+      <c r="B117" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="I117" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J117" s="11" t="s">
         <v>13</v>
@@ -4683,57 +4715,36 @@
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
       <c r="B118" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="C118" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="F118" s="14">
-        <v>2900000</v>
-      </c>
-      <c r="G118" s="15">
-        <v>2861.68</v>
-      </c>
-      <c r="H118" s="16">
-        <v>0.0015365447975</v>
-      </c>
-      <c r="I118" s="15">
-        <v>6.52</v>
+        <v>13</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
-      <c r="B119" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="C119" s="13" t="s">
+      <c r="B119" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="D119" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="F119" s="14">
-        <v>2700000</v>
-      </c>
-      <c r="G119" s="15">
-        <v>2697.65</v>
-      </c>
-      <c r="H119" s="16">
-        <v>0.0014484708539</v>
-      </c>
-      <c r="I119" s="15">
-        <v>6.37</v>
+      <c r="C119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" s="9">
+        <v>15330.95</v>
+      </c>
+      <c r="H119" s="10">
+        <v>0.0070790950577</v>
+      </c>
+      <c r="I119" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J119" s="11" t="s">
         <v>13</v>
@@ -4741,28 +4752,28 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
       <c r="B120" s="12" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D120" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F120" s="14">
-        <v>2500000</v>
+        <v>7500000</v>
       </c>
       <c r="G120" s="15">
-        <v>2469.99</v>
+        <v>7447.33</v>
       </c>
       <c r="H120" s="16">
-        <v>0.0013262315439</v>
+        <v>0.0034388186641</v>
       </c>
       <c r="I120" s="15">
-        <v>6.52</v>
+        <v>5.61</v>
       </c>
       <c r="J120" s="11" t="s">
         <v>13</v>
@@ -4770,28 +4781,28 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
       <c r="B121" s="12" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D121" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F121" s="14">
-        <v>1300000</v>
+        <v>5000000</v>
       </c>
       <c r="G121" s="15">
-        <v>1281.25</v>
+        <v>4991.43</v>
       </c>
       <c r="H121" s="16">
-        <v>0.0006879518401</v>
+        <v>0.0023048022102</v>
       </c>
       <c r="I121" s="15">
-        <v>6.51</v>
+        <v>5.70</v>
       </c>
       <c r="J121" s="11" t="s">
         <v>13</v>
@@ -4799,28 +4810,28 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
       <c r="B122" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C122" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D122" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E122" s="13" t="s">
-        <v>235</v>
-      </c>
       <c r="F122" s="14">
-        <v>100000</v>
+        <v>2100000</v>
       </c>
       <c r="G122" s="15">
-        <v>98.56</v>
+        <v>2096.40</v>
       </c>
       <c r="H122" s="16">
-        <v>0.0000529206114</v>
+        <v>0.0009680166512</v>
       </c>
       <c r="I122" s="15">
-        <v>6.51</v>
+        <v>5.70</v>
       </c>
       <c r="J122" s="11" t="s">
         <v>13</v>
@@ -4828,36 +4839,57 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
       <c r="B123" s="12" t="s">
-        <v>13</v>
+        <v>241</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="F123" s="14">
+        <v>400000</v>
+      </c>
+      <c r="G123" s="15">
+        <v>398.44</v>
+      </c>
+      <c r="H123" s="16">
+        <v>0.0001839804209</v>
+      </c>
+      <c r="I123" s="15">
+        <v>5.70</v>
       </c>
       <c r="J123" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1">
-      <c r="B124" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D124" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F124" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G124" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="H124" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="I124" s="9" t="s">
-        <v>13</v>
+      <c r="B124" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="F124" s="14">
+        <v>200000</v>
+      </c>
+      <c r="G124" s="15">
+        <v>198.78</v>
+      </c>
+      <c r="H124" s="16">
+        <v>0.0000917870396</v>
+      </c>
+      <c r="I124" s="15">
+        <v>5.60</v>
       </c>
       <c r="J124" s="11" t="s">
         <v>13</v>
@@ -4865,35 +4897,35 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1">
       <c r="B125" s="12" t="s">
-        <v>13</v>
+        <v>244</v>
+      </c>
+      <c r="C125" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="F125" s="14">
+        <v>200000</v>
+      </c>
+      <c r="G125" s="15">
+        <v>198.57</v>
+      </c>
+      <c r="H125" s="16">
+        <v>0.0000916900717</v>
+      </c>
+      <c r="I125" s="15">
+        <v>5.61</v>
       </c>
       <c r="J125" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
-      <c r="B126" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D126" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F126" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G126" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="H126" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="I126" s="9" t="s">
+      <c r="B126" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J126" s="11" t="s">
@@ -4901,7 +4933,28 @@
       </c>
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1">
-      <c r="B127" s="12" t="s">
+      <c r="B127" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="I127" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J127" s="11" t="s">
@@ -4909,28 +4962,7 @@
       </c>
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1">
-      <c r="B128" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D128" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E128" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G128" s="9">
-        <v>105328.56</v>
-      </c>
-      <c r="H128" s="10">
-        <v>0.0565549086222</v>
-      </c>
-      <c r="I128" s="9" t="s">
+      <c r="B128" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J128" s="11" t="s">
@@ -4938,7 +4970,28 @@
       </c>
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1">
-      <c r="B129" s="12" t="s">
+      <c r="B129" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="I129" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J129" s="11" t="s">
@@ -4946,28 +4999,7 @@
       </c>
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1">
-      <c r="B130" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D130" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E130" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F130" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G130" s="9">
-        <v>3090.2388055</v>
-      </c>
-      <c r="H130" s="10">
-        <v>0.0016592667104</v>
-      </c>
-      <c r="I130" s="9" t="s">
+      <c r="B130" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J130" s="11" t="s">
@@ -4975,21 +5007,28 @@
       </c>
     </row>
     <row r="131" spans="2:10" ht="15" customHeight="1">
-      <c r="B131" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="C131" s="13"/>
-      <c r="D131" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E131" s="13"/>
-      <c r="G131" s="15">
-        <v>3090.2388055</v>
-      </c>
-      <c r="H131" s="16">
-        <v>0.0016592667104</v>
-      </c>
-      <c r="I131" s="15" t="s">
+      <c r="B131" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="9">
+        <v>90290.75</v>
+      </c>
+      <c r="H131" s="10">
+        <v>0.0416919239915</v>
+      </c>
+      <c r="I131" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J131" s="11" t="s">
@@ -5005,265 +5044,215 @@
       </c>
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1">
-      <c r="B133" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="C133" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D133" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E133" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G133" s="18">
-        <v>-5205.04360206984</v>
-      </c>
-      <c r="H133" s="19">
-        <v>-0.0027947858139338614</v>
-      </c>
-      <c r="I133" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J133" s="20" t="s">
+      <c r="B133" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="9">
+        <v>3090.2388055</v>
+      </c>
+      <c r="H133" s="10">
+        <v>0.0014269235928</v>
+      </c>
+      <c r="I133" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J133" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1">
-      <c r="B134" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="C134" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D134" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E134" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G134" s="18">
-        <v>1862412.34520343</v>
-      </c>
-      <c r="H134" s="19">
-        <v>0.9999999999957658</v>
-      </c>
-      <c r="I134" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J134" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="136" spans="2:8" ht="15" customHeight="1">
+      <c r="B134" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C134" s="13"/>
+      <c r="D134" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="13"/>
+      <c r="G134" s="15">
+        <v>3090.2388055</v>
+      </c>
+      <c r="H134" s="16">
+        <v>0.0014269235928</v>
+      </c>
+      <c r="I134" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J134" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="2:10" ht="15" customHeight="1">
+      <c r="B135" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J135" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="2:10" ht="15" customHeight="1">
       <c r="B136" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="C136" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D136" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E136" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F136" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G136" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H136" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="137" spans="2:8" ht="15" customHeight="1">
+        <v>255</v>
+      </c>
+      <c r="C136" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G136" s="19">
+        <v>5397.987347060349</v>
+      </c>
+      <c r="H136" s="20">
+        <v>0.002492530831577423</v>
+      </c>
+      <c r="I136" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J136" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="2:10" ht="15" customHeight="1">
       <c r="B137" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C137" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D137" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="E137" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F137" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G137" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="H137" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="138" spans="2:8" ht="15" customHeight="1">
-      <c r="B138" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D138" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E138" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F138" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G138" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H138" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="139" spans="2:10" ht="15" customHeight="1">
-      <c r="B139" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="C139" s="13"/>
-      <c r="D139" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E139" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F139" s="14">
-        <v>1834900</v>
-      </c>
-      <c r="G139" s="15">
-        <v>3082.82</v>
-      </c>
-      <c r="H139" s="16">
-        <v>0.0016552832716</v>
-      </c>
-      <c r="I139" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J139" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="143" spans="2:9" ht="15" customHeight="1">
-      <c r="B143" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="C143" s="21"/>
-      <c r="D143" s="21"/>
-      <c r="E143" s="21"/>
-      <c r="F143" s="21"/>
-      <c r="G143" s="21"/>
-      <c r="H143" s="21"/>
-      <c r="I143" s="21"/>
-    </row>
-    <row r="147" spans="2:9" ht="15" customHeight="1">
-      <c r="B147" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C147" s="21"/>
-      <c r="D147" s="21"/>
-      <c r="E147" s="21"/>
-      <c r="F147" s="21"/>
-      <c r="G147" s="21"/>
-      <c r="H147" s="21"/>
-      <c r="I147" s="21"/>
-    </row>
-    <row r="148" spans="2:8" ht="15" customHeight="1">
-      <c r="B148" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="C148" s="21"/>
-      <c r="D148" s="21"/>
-      <c r="E148" s="21"/>
-      <c r="F148" s="21"/>
-      <c r="G148" s="21"/>
-      <c r="H148" s="21"/>
-    </row>
-    <row r="149" spans="2:8" ht="15" customHeight="1">
-      <c r="B149" s="13" t="s">
+      <c r="C137" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D137" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F137" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G137" s="19">
+        <v>2165665.22615256</v>
+      </c>
+      <c r="H137" s="20">
+        <v>0.999999999994177</v>
+      </c>
+      <c r="I137" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J137" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140" spans="2:9" ht="15" customHeight="1">
+      <c r="B140" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="C149" s="21"/>
-      <c r="D149" s="21"/>
-      <c r="E149" s="21"/>
-      <c r="F149" s="21"/>
-      <c r="G149" s="21"/>
-      <c r="H149" s="21"/>
-    </row>
-    <row r="150" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B150" s="22" t="s">
+      <c r="C140" s="22"/>
+      <c r="D140" s="22"/>
+      <c r="E140" s="22"/>
+      <c r="F140" s="22"/>
+      <c r="G140" s="22"/>
+      <c r="H140" s="22"/>
+      <c r="I140" s="22"/>
+    </row>
+    <row r="141" spans="2:8" ht="15" customHeight="1">
+      <c r="B141" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="C150" s="21"/>
-      <c r="D150" s="21"/>
-      <c r="E150" s="21"/>
-      <c r="F150" s="21"/>
-      <c r="G150" s="21"/>
-      <c r="H150" s="21"/>
-    </row>
-    <row r="151" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B151" s="22" t="s">
+      <c r="C141" s="22"/>
+      <c r="D141" s="22"/>
+      <c r="E141" s="22"/>
+      <c r="F141" s="22"/>
+      <c r="G141" s="22"/>
+      <c r="H141" s="22"/>
+    </row>
+    <row r="142" spans="2:8" ht="15" customHeight="1">
+      <c r="B142" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="C151" s="21"/>
-      <c r="D151" s="21"/>
-      <c r="E151" s="21"/>
-      <c r="F151" s="21"/>
-      <c r="G151" s="21"/>
-      <c r="H151" s="21"/>
-    </row>
-    <row r="152" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B152" s="22" t="s">
+      <c r="C142" s="22"/>
+      <c r="D142" s="22"/>
+      <c r="E142" s="22"/>
+      <c r="F142" s="22"/>
+      <c r="G142" s="22"/>
+      <c r="H142" s="22"/>
+    </row>
+    <row r="143" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B143" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="C152" s="21"/>
-      <c r="D152" s="21"/>
-      <c r="E152" s="21"/>
-      <c r="F152" s="21"/>
-      <c r="G152" s="21"/>
-      <c r="H152" s="21"/>
-    </row>
-    <row r="155" ht="15">
-      <c r="B155" s="21" t="s">
+      <c r="C143" s="22"/>
+      <c r="D143" s="22"/>
+      <c r="E143" s="22"/>
+      <c r="F143" s="22"/>
+      <c r="G143" s="22"/>
+      <c r="H143" s="22"/>
+    </row>
+    <row r="144" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B144" s="23" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="170" ht="15">
-      <c r="B170" s="21" t="s">
+      <c r="C144" s="22"/>
+      <c r="D144" s="22"/>
+      <c r="E144" s="22"/>
+      <c r="F144" s="22"/>
+      <c r="G144" s="22"/>
+      <c r="H144" s="22"/>
+    </row>
+    <row r="145" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B145" s="23" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="171" ht="15">
-      <c r="B171" s="21" t="s">
+      <c r="C145" s="22"/>
+      <c r="D145" s="22"/>
+      <c r="E145" s="22"/>
+      <c r="F145" s="22"/>
+      <c r="G145" s="22"/>
+      <c r="H145" s="22"/>
+    </row>
+    <row r="148" ht="15">
+      <c r="B148" s="22" t="s">
         <v>263</v>
       </c>
     </row>
+    <row r="163" ht="15">
+      <c r="B163" s="22" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="164" ht="15">
+      <c r="B164" s="22" t="s">
+        <v>265</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B148:H148"/>
-    <mergeCell ref="B149:H149"/>
-    <mergeCell ref="B150:H150"/>
-    <mergeCell ref="B151:H151"/>
-    <mergeCell ref="B152:H152"/>
+  <mergeCells count="9">
+    <mergeCell ref="B142:H142"/>
+    <mergeCell ref="B143:H143"/>
+    <mergeCell ref="B144:H144"/>
+    <mergeCell ref="B145:H145"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B143:I143"/>
-    <mergeCell ref="B147:I147"/>
+    <mergeCell ref="B140:I140"/>
+    <mergeCell ref="B141:H141"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
